--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/5009-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/5009-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{09FA242D-E7BE-4FA2-ABB1-9EC91A69E8EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3DF499D-E1BB-4846-8774-9191A281AAAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{78AAEF06-B1BA-4344-968F-8318D5463E58}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{A52B776C-9DB3-40A6-8592-7CA5E3DA2D40}"/>
   </bookViews>
   <sheets>
     <sheet name="5009-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1520,30 +1520,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90EE5B8A-48C1-4280-BBFD-A0868D4FAA9A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E935F32-949E-433B-B98E-1BD9CCC1A914}">
   <dimension ref="A1:X69"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1577,7 +1577,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1613,7 +1613,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1733,7 +1733,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1805,7 +1805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>29</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2024</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>8.57</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2247,7 +2247,7 @@
         <v>8.57</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>29</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2023</v>
       </c>
@@ -2615,7 +2615,7 @@
         <v>5.77</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>5.77</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2911,7 +2911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -2985,7 +2985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2022</v>
       </c>
@@ -3057,7 +3057,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>29</v>
       </c>
@@ -3131,7 +3131,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>29</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>29</v>
       </c>
@@ -3279,7 +3279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>29</v>
       </c>
@@ -3353,7 +3353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="35">
         <v>2021</v>
       </c>
@@ -3425,7 +3425,7 @@
         <v>6.97</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>29</v>
       </c>
@@ -3499,7 +3499,7 @@
         <v>6.97</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>29</v>
       </c>
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>29</v>
       </c>
@@ -3647,7 +3647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>29</v>
       </c>
@@ -3721,7 +3721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>2020</v>
       </c>
@@ -3793,7 +3793,7 @@
         <v>2.64</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="16" t="s">
         <v>29</v>
       </c>
@@ -3867,7 +3867,7 @@
         <v>2.64</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="16" t="s">
         <v>29</v>
       </c>
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="16" t="s">
         <v>29</v>
       </c>
@@ -4015,7 +4015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="16" t="s">
         <v>29</v>
       </c>
@@ -4089,7 +4089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="16" t="s">
         <v>29</v>
       </c>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="35">
         <v>2019</v>
       </c>
@@ -4235,7 +4235,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
         <v>29</v>
       </c>
@@ -4309,7 +4309,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="11" t="s">
         <v>29</v>
       </c>
@@ -4383,7 +4383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
         <v>29</v>
       </c>
@@ -4457,7 +4457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="11" t="s">
         <v>29</v>
       </c>
@@ -4531,7 +4531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="37">
         <v>2018</v>
       </c>
@@ -4603,7 +4603,7 @@
         <v>2.71</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="35">
         <v>2017</v>
       </c>
@@ -4675,7 +4675,7 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="37">
         <v>2016</v>
       </c>
@@ -4747,7 +4747,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="35">
         <v>2015</v>
       </c>
@@ -4819,7 +4819,7 @@
         <v>6.62</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="37">
         <v>2014</v>
       </c>
@@ -4891,7 +4891,7 @@
         <v>5.88</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="35">
         <v>2013</v>
       </c>
@@ -4963,7 +4963,7 @@
         <v>2.56</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="37">
         <v>2012</v>
       </c>
@@ -5035,7 +5035,7 @@
         <v>5.39</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="35">
         <v>2011</v>
       </c>
@@ -5107,7 +5107,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="37">
         <v>2010</v>
       </c>
@@ -5179,7 +5179,7 @@
         <v>2.39</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="35">
         <v>2009</v>
       </c>
@@ -5251,7 +5251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="37">
         <v>2008</v>
       </c>
@@ -5323,7 +5323,7 @@
         <v>9.48</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="35">
         <v>2007</v>
       </c>
@@ -5395,7 +5395,7 @@
         <v>26.3</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="37">
         <v>2006</v>
       </c>
@@ -5467,7 +5467,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="35">
         <v>2005</v>
       </c>
@@ -5539,7 +5539,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="37">
         <v>2004</v>
       </c>
@@ -5611,7 +5611,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="58" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="35">
         <v>2003</v>
       </c>
@@ -5683,7 +5683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="37">
         <v>2002</v>
       </c>
@@ -5755,7 +5755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="35">
         <v>2001</v>
       </c>
@@ -5827,7 +5827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A61" s="37">
         <v>2000</v>
       </c>
@@ -5899,7 +5899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A62" s="35">
         <v>1999</v>
       </c>
@@ -5971,7 +5971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A63" s="37">
         <v>1998</v>
       </c>
@@ -6043,7 +6043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A64" s="35">
         <v>1997</v>
       </c>
@@ -6115,7 +6115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A65" s="37">
         <v>1996</v>
       </c>
@@ -6187,7 +6187,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A66" s="35">
         <v>1995</v>
       </c>
@@ -6259,7 +6259,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A67" s="37">
         <v>1994</v>
       </c>
@@ -6331,7 +6331,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A68" s="35">
         <v>1993</v>
       </c>
@@ -6403,7 +6403,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A69" s="37" t="s">
         <v>61</v>
       </c>
